--- a/outputs/marine_equipment/Отгрузка_Питер_учет.xlsx
+++ b/outputs/marine_equipment/Отгрузка_Питер_учет.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Итоги по состоянию" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Отгрузка'!$A$4:$Y$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Отгрузка'!$A$4:$Y$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>SUM('Отгрузка'!N5:N110)</f>
+        <f>SUM('Отгрузка'!N5:N149)</f>
         <v/>
       </c>
     </row>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B20" s="13">
-        <f>SUM('Отгрузка'!O5:O110)</f>
+        <f>SUM('Отгрузка'!O5:O149)</f>
         <v/>
       </c>
     </row>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>SUM('Отгрузка'!L5:L110)</f>
+        <f>SUM('Отгрузка'!L5:L149)</f>
         <v/>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>SUM('Отгрузка'!T5:T110)</f>
+        <f>SUM('Отгрузка'!T5:T149)</f>
         <v/>
       </c>
     </row>
@@ -956,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y111"/>
+  <dimension ref="A1:Y150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5014,25 +5014,29 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Ду300</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 300</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr"/>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду80 Ру6,3</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>521-03.023</t>
+        </is>
+      </c>
       <c r="H47" s="16" t="inlineStr"/>
       <c r="I47" s="16" t="inlineStr">
         <is>
@@ -5041,20 +5045,20 @@
       </c>
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M47" s="16" t="n">
-        <v>230</v>
+        <v>28</v>
       </c>
       <c r="N47" s="17">
         <f>L47*M47</f>
         <v/>
       </c>
       <c r="O47" s="18" t="n">
-        <v>0.35</v>
+        <v>0.06</v>
       </c>
       <c r="P47" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N47/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O47/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L47/'Расходы и доставка'!$B$21,T47/'Расходы и доставка'!$B$22))),0)</f>
@@ -5069,7 +5073,7 @@
         <v/>
       </c>
       <c r="S47" s="21" t="n">
-        <v>400000</v>
+        <v>45000</v>
       </c>
       <c r="T47" s="17">
         <f>L47*S47</f>
@@ -5086,7 +5090,7 @@
       <c r="W47" s="16" t="inlineStr"/>
       <c r="X47" s="4" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="Y47" s="23" t="inlineStr"/>
@@ -5112,19 +5116,15 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду80 Ру6,3</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>521-03.023</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду50</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="16" t="inlineStr"/>
       <c r="I48" s="16" t="inlineStr">
         <is>
@@ -5133,20 +5133,20 @@
       </c>
       <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="4" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="L48" s="16" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="M48" s="16" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="N48" s="17">
         <f>L48*M48</f>
         <v/>
       </c>
       <c r="O48" s="18" t="n">
-        <v>0.06</v>
+        <v>0.792</v>
       </c>
       <c r="P48" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N48/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O48/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L48/'Расходы и доставка'!$B$21,T48/'Расходы и доставка'!$B$22))),0)</f>
@@ -5161,7 +5161,7 @@
         <v/>
       </c>
       <c r="S48" s="21" t="n">
-        <v>45000</v>
+        <v>22500</v>
       </c>
       <c r="T48" s="17">
         <f>L48*S48</f>
@@ -5178,7 +5178,7 @@
       <c r="W48" s="16" t="inlineStr"/>
       <c r="X48" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y48" s="23" t="inlineStr"/>
@@ -5209,10 +5209,14 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr"/>
+          <t>Клапан фланцевый проходной Ду50 Ру25</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>521-01.128</t>
+        </is>
+      </c>
       <c r="H49" s="16" t="inlineStr"/>
       <c r="I49" s="16" t="inlineStr">
         <is>
@@ -5221,10 +5225,10 @@
       </c>
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="L49" s="16" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="M49" s="16" t="n">
         <v>14</v>
@@ -5234,7 +5238,7 @@
         <v/>
       </c>
       <c r="O49" s="18" t="n">
-        <v>0.792</v>
+        <v>0.06</v>
       </c>
       <c r="P49" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N49/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O49/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L49/'Расходы и доставка'!$B$21,T49/'Расходы и доставка'!$B$22))),0)</f>
@@ -5297,12 +5301,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру25</t>
+          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>521-01.128</t>
+          <t>595-01.002</t>
         </is>
       </c>
       <c r="H50" s="16" t="inlineStr"/>
@@ -5313,10 +5317,10 @@
       </c>
       <c r="J50" s="4" t="inlineStr"/>
       <c r="K50" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L50" s="16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M50" s="16" t="n">
         <v>14</v>
@@ -5326,7 +5330,7 @@
         <v/>
       </c>
       <c r="O50" s="18" t="n">
-        <v>0.06</v>
+        <v>0.024</v>
       </c>
       <c r="P50" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N50/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O50/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L50/'Расходы и доставка'!$B$21,T50/'Расходы и доставка'!$B$22))),0)</f>
@@ -5358,7 +5362,7 @@
       <c r="W50" s="16" t="inlineStr"/>
       <c r="X50" s="4" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
       <c r="Y50" s="23" t="inlineStr"/>
@@ -5379,7 +5383,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5389,36 +5393,32 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>595-01.002</t>
-        </is>
-      </c>
+          <t>Захлопка Ду50Ру6 - БРАК</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="16" t="inlineStr"/>
       <c r="I51" s="16" t="inlineStr">
         <is>
-          <t>Комплект</t>
+          <t>Брак</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M51" s="16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N51" s="17">
         <f>L51*M51</f>
         <v/>
       </c>
       <c r="O51" s="18" t="n">
-        <v>0.024</v>
+        <v>0.036</v>
       </c>
       <c r="P51" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N51/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O51/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L51/'Расходы и доставка'!$B$21,T51/'Расходы и доставка'!$B$22))),0)</f>
@@ -5433,7 +5433,7 @@
         <v/>
       </c>
       <c r="S51" s="21" t="n">
-        <v>22500</v>
+        <v>17500</v>
       </c>
       <c r="T51" s="17">
         <f>L51*S51</f>
@@ -5450,7 +5450,7 @@
       <c r="W51" s="16" t="inlineStr"/>
       <c r="X51" s="4" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y51" s="23" t="inlineStr"/>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -5481,32 +5481,32 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Захлопка Ду50Ру6 - БРАК</t>
+          <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="16" t="inlineStr"/>
       <c r="I52" s="16" t="inlineStr">
         <is>
-          <t>Брак</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="4" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="L52" s="16" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="M52" s="16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N52" s="17">
         <f>L52*M52</f>
         <v/>
       </c>
       <c r="O52" s="18" t="n">
-        <v>0.036</v>
+        <v>1.176</v>
       </c>
       <c r="P52" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N52/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O52/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L52/'Расходы и доставка'!$B$21,T52/'Расходы и доставка'!$B$22))),0)</f>
@@ -5521,7 +5521,7 @@
         <v/>
       </c>
       <c r="S52" s="21" t="n">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="T52" s="17">
         <f>L52*S52</f>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
+          <t>Клапан фланцевый проходной Ду65</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
@@ -5581,20 +5581,20 @@
       </c>
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="n">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="L53" s="16" t="n">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="M53" s="16" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N53" s="17">
         <f>L53*M53</f>
         <v/>
       </c>
       <c r="O53" s="18" t="n">
-        <v>1.176</v>
+        <v>0.5</v>
       </c>
       <c r="P53" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N53/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O53/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L53/'Расходы и доставка'!$B$21,T53/'Расходы и доставка'!$B$22))),0)</f>
@@ -5609,7 +5609,7 @@
         <v/>
       </c>
       <c r="S53" s="21" t="n">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="T53" s="17">
         <f>L53*S53</f>
@@ -5626,7 +5626,7 @@
       <c r="W53" s="16" t="inlineStr"/>
       <c r="X53" s="4" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y53" s="23" t="inlineStr"/>
@@ -5657,10 +5657,14 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr"/>
+          <t>Клапан фланцевый проходной Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>521-03.488</t>
+        </is>
+      </c>
       <c r="H54" s="16" t="inlineStr"/>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -5669,10 +5673,10 @@
       </c>
       <c r="J54" s="4" t="inlineStr"/>
       <c r="K54" s="4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L54" s="16" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="M54" s="16" t="n">
         <v>20</v>
@@ -5682,7 +5686,7 @@
         <v/>
       </c>
       <c r="O54" s="18" t="n">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="P54" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N54/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O54/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L54/'Расходы и доставка'!$B$21,T54/'Расходы и доставка'!$B$22))),0)</f>
@@ -5740,17 +5744,17 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду70</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65 Ру10</t>
+          <t>Клапан фланцевый проходной Ду70 Ру10</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>521-03.488</t>
+          <t>521-01.184</t>
         </is>
       </c>
       <c r="H55" s="16" t="inlineStr"/>
@@ -5761,20 +5765,20 @@
       </c>
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L55" s="16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M55" s="16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N55" s="17">
         <f>L55*M55</f>
         <v/>
       </c>
       <c r="O55" s="18" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="P55" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N55/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O55/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L55/'Расходы и доставка'!$B$21,T55/'Расходы и доставка'!$B$22))),0)</f>
@@ -5789,7 +5793,7 @@
         <v/>
       </c>
       <c r="S55" s="21" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="T55" s="17">
         <f>L55*S55</f>
@@ -5842,7 +5846,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>521-01.184</t>
+          <t>522-01.226</t>
         </is>
       </c>
       <c r="H56" s="16" t="inlineStr"/>
@@ -5853,10 +5857,10 @@
       </c>
       <c r="J56" s="4" t="inlineStr"/>
       <c r="K56" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L56" s="16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M56" s="16" t="n">
         <v>23</v>
@@ -5866,7 +5870,7 @@
         <v/>
       </c>
       <c r="O56" s="18" t="n">
-        <v>0.11</v>
+        <v>0.044</v>
       </c>
       <c r="P56" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N56/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O56/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L56/'Расходы и доставка'!$B$21,T56/'Расходы и доставка'!$B$22))),0)</f>
@@ -5924,41 +5928,37 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Ду70</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду70 Ру10</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>522-01.226</t>
-        </is>
-      </c>
+          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="16" t="inlineStr"/>
       <c r="I57" s="16" t="inlineStr">
         <is>
-          <t>Комплект</t>
+          <t>Брак</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L57" s="16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M57" s="16" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="N57" s="17">
         <f>L57*M57</f>
         <v/>
       </c>
       <c r="O57" s="18" t="n">
-        <v>0.044</v>
+        <v>0.096</v>
       </c>
       <c r="P57" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N57/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O57/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L57/'Расходы и доставка'!$B$21,T57/'Расходы и доставка'!$B$22))),0)</f>
@@ -5973,7 +5973,7 @@
         <v/>
       </c>
       <c r="S57" s="21" t="n">
-        <v>30000</v>
+        <v>18000</v>
       </c>
       <c r="T57" s="17">
         <f>L57*S57</f>
@@ -5990,7 +5990,7 @@
       <c r="W57" s="16" t="inlineStr"/>
       <c r="X57" s="4" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y57" s="23" t="inlineStr"/>
@@ -6016,37 +6016,37 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду50 - БРАК</t>
+          <t>Клапан фланцевый проходной Ду80</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="16" t="inlineStr"/>
       <c r="I58" s="16" t="inlineStr">
         <is>
-          <t>Брак</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr"/>
       <c r="K58" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L58" s="16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M58" s="16" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="N58" s="17">
         <f>L58*M58</f>
         <v/>
       </c>
       <c r="O58" s="18" t="n">
-        <v>0.096</v>
+        <v>0.18</v>
       </c>
       <c r="P58" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N58/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O58/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L58/'Расходы и доставка'!$B$21,T58/'Расходы и доставка'!$B$22))),0)</f>
@@ -6061,7 +6061,7 @@
         <v/>
       </c>
       <c r="S58" s="21" t="n">
-        <v>18000</v>
+        <v>36000</v>
       </c>
       <c r="T58" s="17">
         <f>L58*S58</f>
@@ -6078,7 +6078,7 @@
       <c r="W58" s="16" t="inlineStr"/>
       <c r="X58" s="4" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y58" s="23" t="inlineStr"/>
@@ -6094,22 +6094,18 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Ду80</t>
-        </is>
-      </c>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду80</t>
+          <t>Электропривод к задвижке</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
@@ -6121,20 +6117,20 @@
       </c>
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L59" s="16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M59" s="16" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N59" s="17">
         <f>L59*M59</f>
         <v/>
       </c>
       <c r="O59" s="18" t="n">
-        <v>0.18</v>
+        <v>0.01</v>
       </c>
       <c r="P59" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N59/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O59/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L59/'Расходы и доставка'!$B$21,T59/'Расходы и доставка'!$B$22))),0)</f>
@@ -6149,7 +6145,7 @@
         <v/>
       </c>
       <c r="S59" s="21" t="n">
-        <v>36000</v>
+        <v>50000</v>
       </c>
       <c r="T59" s="17">
         <f>L59*S59</f>
@@ -6166,7 +6162,7 @@
       <c r="W59" s="16" t="inlineStr"/>
       <c r="X59" s="4" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Гараж 2</t>
         </is>
       </c>
       <c r="Y59" s="23" t="inlineStr"/>
@@ -6182,18 +6178,22 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr"/>
+          <t>фильтр забортной воды</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Ду100</t>
+        </is>
+      </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Электропривод к задвижке</t>
+          <t>Сетка на фильтр Ду100 или Ду80</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
@@ -6205,20 +6205,20 @@
       </c>
       <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M60" s="16" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="N60" s="17">
         <f>L60*M60</f>
         <v/>
       </c>
       <c r="O60" s="18" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="P60" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N60/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O60/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L60/'Расходы и доставка'!$B$21,T60/'Расходы и доставка'!$B$22))),0)</f>
@@ -6233,7 +6233,7 @@
         <v/>
       </c>
       <c r="S60" s="21" t="n">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="T60" s="17">
         <f>L60*S60</f>
@@ -6250,7 +6250,7 @@
       <c r="W60" s="16" t="inlineStr"/>
       <c r="X60" s="4" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="Y60" s="23" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду100 или Ду80</t>
+          <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
@@ -6354,22 +6354,22 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду200</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
+          <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
@@ -6381,20 +6381,20 @@
       </c>
       <c r="J62" s="4" t="inlineStr"/>
       <c r="K62" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M62" s="16" t="n">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="N62" s="17">
         <f>L62*M62</f>
         <v/>
       </c>
       <c r="O62" s="18" t="n">
-        <v>0.09</v>
+        <v>0.48</v>
       </c>
       <c r="P62" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N62/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O62/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L62/'Расходы и доставка'!$B$21,T62/'Расходы и доставка'!$B$22))),0)</f>
@@ -6409,7 +6409,7 @@
         <v/>
       </c>
       <c r="S62" s="21" t="n">
-        <v>10000</v>
+        <v>150000</v>
       </c>
       <c r="T62" s="17">
         <f>L62*S62</f>
@@ -6426,7 +6426,7 @@
       <c r="W62" s="16" t="inlineStr"/>
       <c r="X62" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y62" s="23" t="inlineStr"/>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Ду200</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200</t>
+          <t>Клапан фланцевый проходной Ду 80 Ру 10, 521 -35.3451</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
@@ -6469,20 +6469,20 @@
       </c>
       <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L63" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M63" s="16" t="n">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="N63" s="17">
         <f>L63*M63</f>
         <v/>
       </c>
       <c r="O63" s="18" t="n">
-        <v>0.48</v>
+        <v>0.03</v>
       </c>
       <c r="P63" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N63/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O63/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L63/'Расходы и доставка'!$B$21,T63/'Расходы и доставка'!$B$22))),0)</f>
@@ -6497,7 +6497,7 @@
         <v/>
       </c>
       <c r="S63" s="21" t="n">
-        <v>150000</v>
+        <v>32000</v>
       </c>
       <c r="T63" s="17">
         <f>L63*S63</f>
@@ -6530,25 +6530,29 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду 80 Ру 10, 521 -35.3451</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr"/>
+          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>529-35.1406-01</t>
+        </is>
+      </c>
       <c r="H64" s="16" t="inlineStr"/>
       <c r="I64" s="16" t="inlineStr">
         <is>
@@ -6563,14 +6567,14 @@
         <v>1</v>
       </c>
       <c r="M64" s="16" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="N64" s="17">
         <f>L64*M64</f>
         <v/>
       </c>
       <c r="O64" s="18" t="n">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
       <c r="P64" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N64/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O64/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L64/'Расходы и доставка'!$B$21,T64/'Расходы и доставка'!$B$22))),0)</f>
@@ -6585,7 +6589,7 @@
         <v/>
       </c>
       <c r="S64" s="21" t="n">
-        <v>32000</v>
+        <v>40000</v>
       </c>
       <c r="T64" s="17">
         <f>L64*S64</f>
@@ -6602,7 +6606,7 @@
       <c r="W64" s="16" t="inlineStr"/>
       <c r="X64" s="4" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="Y64" s="23" t="inlineStr"/>
@@ -6633,12 +6637,12 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
+          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>529-35.1406-01</t>
+          <t>529-03.074</t>
         </is>
       </c>
       <c r="H65" s="16" t="inlineStr"/>
@@ -6649,10 +6653,10 @@
       </c>
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L65" s="16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M65" s="16" t="n">
         <v>35</v>
@@ -6662,7 +6666,7 @@
         <v/>
       </c>
       <c r="O65" s="18" t="n">
-        <v>0.045</v>
+        <v>0.135</v>
       </c>
       <c r="P65" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N65/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O65/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L65/'Расходы и доставка'!$B$21,T65/'Расходы и доставка'!$B$22))),0)</f>
@@ -6725,12 +6729,12 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
+          <t>Захлопка фланцевая вертикальная Ду100</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>529-03.074</t>
+          <t>529-03.003</t>
         </is>
       </c>
       <c r="H66" s="16" t="inlineStr"/>
@@ -6741,10 +6745,10 @@
       </c>
       <c r="J66" s="4" t="inlineStr"/>
       <c r="K66" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L66" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M66" s="16" t="n">
         <v>35</v>
@@ -6754,7 +6758,7 @@
         <v/>
       </c>
       <c r="O66" s="18" t="n">
-        <v>0.135</v>
+        <v>0.045</v>
       </c>
       <c r="P66" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N66/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O66/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L66/'Расходы и доставка'!$B$21,T66/'Расходы и доставка'!$B$22))),0)</f>
@@ -6817,12 +6821,12 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду100</t>
+          <t>Захлопка фланцевая угловая Ду100Ру10</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>529-03.003</t>
+          <t>529-35-1405-01</t>
         </is>
       </c>
       <c r="H67" s="16" t="inlineStr"/>
@@ -6899,24 +6903,20 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду60</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая угловая Ду100Ру10</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>529-35-1405-01</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду60</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="16" t="inlineStr"/>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -6931,14 +6931,14 @@
         <v>1</v>
       </c>
       <c r="M68" s="16" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="N68" s="17">
         <f>L68*M68</f>
         <v/>
       </c>
       <c r="O68" s="18" t="n">
-        <v>0.045</v>
+        <v>0.02</v>
       </c>
       <c r="P68" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N68/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O68/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L68/'Расходы и доставка'!$B$21,T68/'Расходы и доставка'!$B$22))),0)</f>
@@ -6953,7 +6953,7 @@
         <v/>
       </c>
       <c r="S68" s="21" t="n">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="T68" s="17">
         <f>L68*S68</f>
@@ -6970,7 +6970,7 @@
       <c r="W68" s="16" t="inlineStr"/>
       <c r="X68" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y68" s="23" t="inlineStr"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Ду60</t>
+          <t>Ду200</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
+          <t>Клинкет Ду 200</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
@@ -7013,20 +7013,20 @@
       </c>
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L69" s="16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M69" s="16" t="n">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="N69" s="17">
         <f>L69*M69</f>
         <v/>
       </c>
       <c r="O69" s="18" t="n">
-        <v>0.02</v>
+        <v>1.76</v>
       </c>
       <c r="P69" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N69/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O69/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L69/'Расходы и доставка'!$B$21,T69/'Расходы и доставка'!$B$22))),0)</f>
@@ -7041,7 +7041,7 @@
         <v/>
       </c>
       <c r="S69" s="21" t="n">
-        <v>18000</v>
+        <v>150000</v>
       </c>
       <c r="T69" s="17">
         <f>L69*S69</f>
@@ -7058,7 +7058,7 @@
       <c r="W69" s="16" t="inlineStr"/>
       <c r="X69" s="4" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Фойе</t>
         </is>
       </c>
       <c r="Y69" s="23" t="inlineStr"/>
@@ -7074,22 +7074,22 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Ярус 1, на настил</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Ду200</t>
+          <t>Ду150</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Клинкет Ду 200</t>
+          <t>Клапан фланцевый проходной Ду150</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
@@ -7101,20 +7101,20 @@
       </c>
       <c r="J70" s="4" t="inlineStr"/>
       <c r="K70" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L70" s="16" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M70" s="16" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="N70" s="17">
         <f>L70*M70</f>
         <v/>
       </c>
       <c r="O70" s="18" t="n">
-        <v>1.76</v>
+        <v>0.2</v>
       </c>
       <c r="P70" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N70/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O70/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L70/'Расходы и доставка'!$B$21,T70/'Расходы и доставка'!$B$22))),0)</f>
@@ -7129,7 +7129,7 @@
         <v/>
       </c>
       <c r="S70" s="21" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="T70" s="17">
         <f>L70*S70</f>
@@ -7146,7 +7146,7 @@
       <c r="W70" s="16" t="inlineStr"/>
       <c r="X70" s="4" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y70" s="23" t="inlineStr"/>
@@ -7172,12 +7172,12 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Ду150</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду150</t>
+          <t>Клапан фланцевый проходной Ду100 Ру10</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
@@ -7189,20 +7189,20 @@
       </c>
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L71" s="16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M71" s="16" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="N71" s="17">
         <f>L71*M71</f>
         <v/>
       </c>
       <c r="O71" s="18" t="n">
-        <v>0.2</v>
+        <v>0.225</v>
       </c>
       <c r="P71" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N71/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O71/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L71/'Расходы и доставка'!$B$21,T71/'Расходы и доставка'!$B$22))),0)</f>
@@ -7217,7 +7217,7 @@
         <v/>
       </c>
       <c r="S71" s="21" t="n">
-        <v>80000</v>
+        <v>42000</v>
       </c>
       <c r="T71" s="17">
         <f>L71*S71</f>
@@ -7260,15 +7260,19 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду200</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду100 Ру10</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr"/>
+          <t>Клапан фланцевый проходной Ду200 Ру6</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>522-03.184</t>
+        </is>
+      </c>
       <c r="H72" s="16" t="inlineStr"/>
       <c r="I72" s="16" t="inlineStr">
         <is>
@@ -7277,20 +7281,20 @@
       </c>
       <c r="J72" s="4" t="inlineStr"/>
       <c r="K72" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L72" s="16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M72" s="16" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="N72" s="17">
         <f>L72*M72</f>
         <v/>
       </c>
       <c r="O72" s="18" t="n">
-        <v>0.225</v>
+        <v>0.16</v>
       </c>
       <c r="P72" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N72/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O72/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L72/'Расходы и доставка'!$B$21,T72/'Расходы и доставка'!$B$22))),0)</f>
@@ -7305,7 +7309,7 @@
         <v/>
       </c>
       <c r="S72" s="21" t="n">
-        <v>42000</v>
+        <v>120000</v>
       </c>
       <c r="T72" s="17">
         <f>L72*S72</f>
@@ -7338,27 +7342,27 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>кингстон</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Ду200</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200 Ру6</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>522-03.184</t>
+          <t>527-03.055</t>
         </is>
       </c>
       <c r="H73" s="16" t="inlineStr"/>
@@ -7369,20 +7373,20 @@
       </c>
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M73" s="16" t="n">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="N73" s="17">
         <f>L73*M73</f>
         <v/>
       </c>
       <c r="O73" s="18" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="P73" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N73/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O73/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L73/'Расходы и доставка'!$B$21,T73/'Расходы и доставка'!$B$22))),0)</f>
@@ -7397,7 +7401,7 @@
         <v/>
       </c>
       <c r="S73" s="21" t="n">
-        <v>120000</v>
+        <v>32000</v>
       </c>
       <c r="T73" s="17">
         <f>L73*S73</f>
@@ -7435,46 +7439,42 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
+          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="16" t="inlineStr"/>
       <c r="I74" s="16" t="inlineStr">
         <is>
-          <t>Комплект</t>
+          <t>Брак</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr"/>
       <c r="K74" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L74" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M74" s="16" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N74" s="17">
         <f>L74*M74</f>
         <v/>
       </c>
       <c r="O74" s="18" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="P74" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N74/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O74/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L74/'Расходы и доставка'!$B$21,T74/'Расходы и доставка'!$B$22))),0)</f>
@@ -7489,7 +7489,7 @@
         <v/>
       </c>
       <c r="S74" s="21" t="n">
-        <v>32000</v>
+        <v>18000</v>
       </c>
       <c r="T74" s="17">
         <f>L74*S74</f>
@@ -7506,7 +7506,7 @@
       <c r="W74" s="16" t="inlineStr"/>
       <c r="X74" s="4" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y74" s="23" t="inlineStr"/>
@@ -7527,24 +7527,28 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>кингстон</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr"/>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>без чертежа</t>
+        </is>
+      </c>
       <c r="H75" s="16" t="inlineStr"/>
       <c r="I75" s="16" t="inlineStr">
         <is>
-          <t>Брак</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr"/>
@@ -7562,7 +7566,7 @@
         <v/>
       </c>
       <c r="O75" s="18" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="P75" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N75/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O75/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L75/'Расходы и доставка'!$B$21,T75/'Расходы и доставка'!$B$22))),0)</f>
@@ -7577,7 +7581,7 @@
         <v/>
       </c>
       <c r="S75" s="21" t="n">
-        <v>18000</v>
+        <v>17500</v>
       </c>
       <c r="T75" s="17">
         <f>L75*S75</f>
@@ -7594,7 +7598,7 @@
       <c r="W75" s="16" t="inlineStr"/>
       <c r="X75" s="4" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y75" s="23" t="inlineStr"/>
@@ -7630,7 +7634,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>без чертежа</t>
+          <t>527-03.054</t>
         </is>
       </c>
       <c r="H76" s="16" t="inlineStr"/>
@@ -7702,51 +7706,47 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>527-03.054</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="16" t="inlineStr"/>
       <c r="I77" s="16" t="inlineStr">
         <is>
-          <t>Комплект</t>
+          <t>Не комплект</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" s="16" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="N77" s="17">
         <f>L77*M77</f>
         <v/>
       </c>
       <c r="O77" s="18" t="n">
-        <v>0.012</v>
+        <v>0.06</v>
       </c>
       <c r="P77" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N77/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O77/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L77/'Расходы и доставка'!$B$21,T77/'Расходы и доставка'!$B$22))),0)</f>
@@ -7761,7 +7761,7 @@
         <v/>
       </c>
       <c r="S77" s="21" t="n">
-        <v>17500</v>
+        <v>24000</v>
       </c>
       <c r="T77" s="17">
         <f>L77*S77</f>
@@ -7778,7 +7778,7 @@
       <c r="W77" s="16" t="inlineStr"/>
       <c r="X77" s="4" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y77" s="23" t="inlineStr"/>
@@ -7799,42 +7799,42 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
+          <t>Клапана невозвратный проходной фланцевый Ду100 Ру10 (522-03.205)</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="16" t="inlineStr"/>
       <c r="I78" s="16" t="inlineStr">
         <is>
-          <t>Не комплект</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr"/>
       <c r="K78" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L78" s="16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M78" s="16" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N78" s="17">
         <f>L78*M78</f>
         <v/>
       </c>
       <c r="O78" s="18" t="n">
-        <v>0.06</v>
+        <v>0.225</v>
       </c>
       <c r="P78" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N78/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O78/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L78/'Расходы и доставка'!$B$21,T78/'Расходы и доставка'!$B$22))),0)</f>
@@ -7849,7 +7849,7 @@
         <v/>
       </c>
       <c r="S78" s="21" t="n">
-        <v>24000</v>
+        <v>34000</v>
       </c>
       <c r="T78" s="17">
         <f>L78*S78</f>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Клапана невозвратный проходной фланцевый Ду100 Ру10 (522-03.205)</t>
+          <t>Клапан фланцевый проходной Ду125</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
@@ -7909,20 +7909,20 @@
       </c>
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L79" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M79" s="16" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N79" s="17">
         <f>L79*M79</f>
         <v/>
       </c>
       <c r="O79" s="18" t="n">
-        <v>0.225</v>
+        <v>0.42</v>
       </c>
       <c r="P79" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N79/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O79/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L79/'Расходы и доставка'!$B$21,T79/'Расходы и доставка'!$B$22))),0)</f>
@@ -7937,7 +7937,7 @@
         <v/>
       </c>
       <c r="S79" s="21" t="n">
-        <v>34000</v>
+        <v>46000</v>
       </c>
       <c r="T79" s="17">
         <f>L79*S79</f>
@@ -7954,7 +7954,7 @@
       <c r="W79" s="16" t="inlineStr"/>
       <c r="X79" s="4" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y79" s="23" t="inlineStr"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125</t>
+          <t>Клапан фланцевый проходной Ду125 Ру10</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
@@ -7997,10 +7997,10 @@
       </c>
       <c r="J80" s="4" t="inlineStr"/>
       <c r="K80" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L80" s="16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M80" s="16" t="n">
         <v>55</v>
@@ -8010,7 +8010,7 @@
         <v/>
       </c>
       <c r="O80" s="18" t="n">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
       <c r="P80" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N80/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O80/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L80/'Расходы и доставка'!$B$21,T80/'Расходы и доставка'!$B$22))),0)</f>
@@ -8063,42 +8063,46 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 Ру10</t>
+          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
-      <c r="H81" s="16" t="inlineStr"/>
+      <c r="H81" s="16" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
-          <t>Комплект</t>
+          <t>Не комплект</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L81" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M81" s="16" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N81" s="17">
         <f>L81*M81</f>
         <v/>
       </c>
       <c r="O81" s="18" t="n">
-        <v>0.21</v>
+        <v>0.045</v>
       </c>
       <c r="P81" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N81/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O81/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L81/'Расходы и доставка'!$B$21,T81/'Расходы и доставка'!$B$22))),0)</f>
@@ -8113,7 +8117,7 @@
         <v/>
       </c>
       <c r="S81" s="21" t="n">
-        <v>46000</v>
+        <v>35000</v>
       </c>
       <c r="T81" s="17">
         <f>L81*S81</f>
@@ -8130,7 +8134,7 @@
       <c r="W81" s="16" t="inlineStr"/>
       <c r="X81" s="4" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y81" s="23" t="inlineStr"/>
@@ -8151,46 +8155,46 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr"/>
-      <c r="H82" s="16" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>521-35.3455-02</t>
+        </is>
+      </c>
+      <c r="H82" s="16" t="inlineStr"/>
       <c r="I82" s="16" t="inlineStr">
         <is>
-          <t>Не комплект</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr"/>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L82" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M82" s="16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N82" s="17">
         <f>L82*M82</f>
         <v/>
       </c>
       <c r="O82" s="18" t="n">
-        <v>0.045</v>
+        <v>0.14</v>
       </c>
       <c r="P82" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N82/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O82/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L82/'Расходы и доставка'!$B$21,T82/'Расходы и доставка'!$B$22))),0)</f>
@@ -8205,7 +8209,7 @@
         <v/>
       </c>
       <c r="S82" s="21" t="n">
-        <v>35000</v>
+        <v>37500</v>
       </c>
       <c r="T82" s="17">
         <f>L82*S82</f>
@@ -8222,7 +8226,7 @@
       <c r="W82" s="16" t="inlineStr"/>
       <c r="X82" s="4" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="Y82" s="23" t="inlineStr"/>
@@ -8253,26 +8257,22 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>521-35.3455-02</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="16" t="inlineStr"/>
       <c r="I83" s="16" t="inlineStr">
         <is>
-          <t>Комплект</t>
+          <t>Не комплект</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L83" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M83" s="16" t="n">
         <v>55</v>
@@ -8282,7 +8282,7 @@
         <v/>
       </c>
       <c r="O83" s="18" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P83" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N83/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O83/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L83/'Расходы и доставка'!$B$21,T83/'Расходы и доставка'!$B$22))),0)</f>
@@ -8297,7 +8297,7 @@
         <v/>
       </c>
       <c r="S83" s="21" t="n">
-        <v>37500</v>
+        <v>30000</v>
       </c>
       <c r="T83" s="17">
         <f>L83*S83</f>
@@ -8314,7 +8314,7 @@
       <c r="W83" s="16" t="inlineStr"/>
       <c r="X83" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="Y83" s="23" t="inlineStr"/>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -8340,37 +8340,37 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="16" t="inlineStr"/>
       <c r="I84" s="16" t="inlineStr">
         <is>
-          <t>Не комплект</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr"/>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L84" s="16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M84" s="16" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="N84" s="17">
         <f>L84*M84</f>
         <v/>
       </c>
       <c r="O84" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="P84" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N84/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O84/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L84/'Расходы и доставка'!$B$21,T84/'Расходы и доставка'!$B$22))),0)</f>
@@ -8385,7 +8385,7 @@
         <v/>
       </c>
       <c r="S84" s="21" t="n">
-        <v>30000</v>
+        <v>7500</v>
       </c>
       <c r="T84" s="17">
         <f>L84*S84</f>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
@@ -8445,20 +8445,20 @@
       </c>
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L85" s="16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M85" s="16" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N85" s="17">
         <f>L85*M85</f>
         <v/>
       </c>
       <c r="O85" s="18" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="P85" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N85/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O85/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L85/'Расходы и доставка'!$B$21,T85/'Расходы и доставка'!$B$22))),0)</f>
@@ -8473,7 +8473,7 @@
         <v/>
       </c>
       <c r="S85" s="21" t="n">
-        <v>7500</v>
+        <v>9750</v>
       </c>
       <c r="T85" s="17">
         <f>L85*S85</f>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
@@ -8533,10 +8533,10 @@
       </c>
       <c r="J86" s="4" t="inlineStr"/>
       <c r="K86" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L86" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86" s="16" t="n">
         <v>20</v>
@@ -8546,7 +8546,7 @@
         <v/>
       </c>
       <c r="O86" s="18" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="P86" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N86/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O86/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L86/'Расходы и доставка'!$B$21,T86/'Расходы и доставка'!$B$22))),0)</f>
@@ -8599,20 +8599,20 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>Ду65</t>
-        </is>
-      </c>
+          <t>прочая арматура</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr"/>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr"/>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>587-182.126</t>
+        </is>
+      </c>
       <c r="H87" s="16" t="inlineStr"/>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -8627,14 +8627,14 @@
         <v>1</v>
       </c>
       <c r="M87" s="16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N87" s="17">
         <f>L87*M87</f>
         <v/>
       </c>
       <c r="O87" s="18" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="P87" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N87/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O87/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L87/'Расходы и доставка'!$B$21,T87/'Расходы и доставка'!$B$22))),0)</f>
@@ -8648,9 +8648,7 @@
         <f>IFERROR(Q87/L87,0)</f>
         <v/>
       </c>
-      <c r="S87" s="21" t="n">
-        <v>9750</v>
-      </c>
+      <c r="S87" s="21" t="n"/>
       <c r="T87" s="17">
         <f>L87*S87</f>
         <v/>
@@ -8666,7 +8664,7 @@
       <c r="W87" s="16" t="inlineStr"/>
       <c r="X87" s="4" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="Y87" s="23" t="inlineStr"/>
@@ -8693,15 +8691,15 @@
       <c r="E88" s="4" t="inlineStr"/>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Клапан</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>587-182.126</t>
-        </is>
-      </c>
-      <c r="H88" s="16" t="inlineStr"/>
+          <t>Клапан фреоновый саленоидный</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr"/>
+      <c r="H88" s="16" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
       <c r="I88" s="16" t="inlineStr">
         <is>
           <t>Комплект</t>
@@ -8709,10 +8707,10 @@
       </c>
       <c r="J88" s="4" t="inlineStr"/>
       <c r="K88" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M88" s="16" t="n">
         <v>5</v>
@@ -8722,7 +8720,7 @@
         <v/>
       </c>
       <c r="O88" s="18" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="P88" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N88/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O88/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L88/'Расходы и доставка'!$B$21,T88/'Расходы и доставка'!$B$22))),0)</f>
@@ -8776,18 +8774,22 @@
           <t>прочая арматура</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Ду65</t>
+        </is>
+      </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr"/>
-      <c r="H89" s="16" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
+          <t>Клапан паровой Ду65Ру10</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>581-03.034</t>
+        </is>
+      </c>
+      <c r="H89" s="16" t="inlineStr"/>
       <c r="I89" s="16" t="inlineStr">
         <is>
           <t>Комплект</t>
@@ -8795,10 +8797,10 @@
       </c>
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L89" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M89" s="16" t="n">
         <v>5</v>
@@ -8859,22 +8861,22 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Клапан паровой Ду65Ру10</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>581-03.034</t>
+          <t>595-3М-48</t>
         </is>
       </c>
       <c r="H90" s="16" t="inlineStr"/>
@@ -8891,14 +8893,14 @@
         <v>1</v>
       </c>
       <c r="M90" s="16" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N90" s="17">
         <f>L90*M90</f>
         <v/>
       </c>
       <c r="O90" s="18" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="P90" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N90/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O90/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L90/'Расходы и доставка'!$B$21,T90/'Расходы и доставка'!$B$22))),0)</f>
@@ -8964,7 +8966,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>595-3М-48</t>
+          <t>595-35-021</t>
         </is>
       </c>
       <c r="H91" s="16" t="inlineStr"/>
@@ -9039,22 +9041,18 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
+          <t>прочая арматура</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>595-35-021</t>
+          <t>2619802505</t>
         </is>
       </c>
       <c r="H92" s="16" t="inlineStr"/>
@@ -9071,14 +9069,14 @@
         <v>1</v>
       </c>
       <c r="M92" s="16" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N92" s="17">
         <f>L92*M92</f>
         <v/>
       </c>
       <c r="O92" s="18" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="P92" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N92/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O92/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L92/'Расходы и доставка'!$B$21,T92/'Расходы и доставка'!$B$22))),0)</f>
@@ -9135,15 +9133,15 @@
       <c r="E93" s="4" t="inlineStr"/>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>2619802505</t>
-        </is>
-      </c>
-      <c r="H93" s="16" t="inlineStr"/>
+          <t>Клапан электромагнитный б/у</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr"/>
+      <c r="H93" s="16" t="inlineStr">
+        <is>
+          <t>Б/у</t>
+        </is>
+      </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
           <t>Комплект</t>
@@ -9151,10 +9149,10 @@
       </c>
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L93" s="16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M93" s="16" t="n">
         <v>5</v>
@@ -9164,7 +9162,7 @@
         <v/>
       </c>
       <c r="O93" s="18" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="P93" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N93/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O93/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L93/'Расходы и доставка'!$B$21,T93/'Расходы и доставка'!$B$22))),0)</f>
@@ -9194,7 +9192,7 @@
       <c r="W93" s="16" t="inlineStr"/>
       <c r="X93" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y93" s="23" t="inlineStr"/>
@@ -9205,7 +9203,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>4. Прочее, по цене за килограмм</t>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -9215,21 +9213,25 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr"/>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Клапан электромагнитный б/у</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr"/>
-      <c r="H94" s="16" t="inlineStr">
-        <is>
-          <t>Б/у</t>
-        </is>
-      </c>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>521-01.465-01</t>
+        </is>
+      </c>
+      <c r="H94" s="16" t="inlineStr"/>
       <c r="I94" s="16" t="inlineStr">
         <is>
           <t>Комплект</t>
@@ -9237,20 +9239,20 @@
       </c>
       <c r="J94" s="4" t="inlineStr"/>
       <c r="K94" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L94" s="16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M94" s="16" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="N94" s="17">
         <f>L94*M94</f>
         <v/>
       </c>
       <c r="O94" s="18" t="n">
-        <v>0.04</v>
+        <v>0.001</v>
       </c>
       <c r="P94" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N94/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O94/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L94/'Расходы и доставка'!$B$21,T94/'Расходы и доставка'!$B$22))),0)</f>
@@ -9264,7 +9266,9 @@
         <f>IFERROR(Q94/L94,0)</f>
         <v/>
       </c>
-      <c r="S94" s="21" t="n"/>
+      <c r="S94" s="21" t="n">
+        <v>20200</v>
+      </c>
       <c r="T94" s="17">
         <f>L94*S94</f>
         <v/>
@@ -9280,7 +9284,7 @@
       <c r="W94" s="16" t="inlineStr"/>
       <c r="X94" s="4" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="Y94" s="23" t="inlineStr"/>
@@ -9306,17 +9310,17 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду6</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>521-01.465-01</t>
+          <t>524-03.004</t>
         </is>
       </c>
       <c r="H95" s="16" t="inlineStr"/>
@@ -9333,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="M95" s="16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="N95" s="17">
         <f>L95*M95</f>
@@ -9355,7 +9359,7 @@
         <v/>
       </c>
       <c r="S95" s="21" t="n">
-        <v>20200</v>
+        <v>9000</v>
       </c>
       <c r="T95" s="17">
         <f>L95*S95</f>
@@ -9398,20 +9402,24 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Ду6</t>
+          <t>Ду3</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
+          <t>Клапан для манометра штущерный Ду3Ру400 новый</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>524-03.004</t>
-        </is>
-      </c>
-      <c r="H96" s="16" t="inlineStr"/>
+          <t>521-03.406</t>
+        </is>
+      </c>
+      <c r="H96" s="16" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
           <t>Комплект</t>
@@ -9419,13 +9427,13 @@
       </c>
       <c r="J96" s="4" t="inlineStr"/>
       <c r="K96" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L96" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M96" s="16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N96" s="17">
         <f>L96*M96</f>
@@ -9447,7 +9455,7 @@
         <v/>
       </c>
       <c r="S96" s="21" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="T96" s="17">
         <f>L96*S96</f>
@@ -9490,17 +9498,17 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Ду3</t>
+          <t>Ду6</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный Ду3Ру400 новый</t>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 новый</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>521-03.406</t>
+          <t>521-02.013</t>
         </is>
       </c>
       <c r="H97" s="16" t="inlineStr">
@@ -9515,20 +9523,20 @@
       </c>
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="L97" s="16" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="M97" s="16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N97" s="17">
         <f>L97*M97</f>
         <v/>
       </c>
       <c r="O97" s="18" t="n">
-        <v>0.001</v>
+        <v>0.048</v>
       </c>
       <c r="P97" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N97/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O97/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L97/'Расходы и доставка'!$B$21,T97/'Расходы и доставка'!$B$22))),0)</f>
@@ -9543,7 +9551,7 @@
         <v/>
       </c>
       <c r="S97" s="21" t="n">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="T97" s="17">
         <f>L97*S97</f>
@@ -9591,7 +9599,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 новый</t>
+          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -9601,7 +9609,7 @@
       </c>
       <c r="H98" s="16" t="inlineStr">
         <is>
-          <t>Новое</t>
+          <t>Б/у</t>
         </is>
       </c>
       <c r="I98" s="16" t="inlineStr">
@@ -9611,10 +9619,10 @@
       </c>
       <c r="J98" s="4" t="inlineStr"/>
       <c r="K98" s="4" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="L98" s="16" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="M98" s="16" t="n">
         <v>0.4</v>
@@ -9624,7 +9632,7 @@
         <v/>
       </c>
       <c r="O98" s="18" t="n">
-        <v>0.048</v>
+        <v>0.001</v>
       </c>
       <c r="P98" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N98/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O98/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L98/'Расходы и доставка'!$B$21,T98/'Расходы и доставка'!$B$22))),0)</f>
@@ -9692,7 +9700,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>521-02.013</t>
+          <t>521-02.014</t>
         </is>
       </c>
       <c r="H99" s="16" t="inlineStr">
@@ -9783,19 +9791,15 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>521-02.014</t>
-        </is>
-      </c>
-      <c r="H100" s="16" t="inlineStr">
-        <is>
-          <t>Б/у</t>
-        </is>
-      </c>
+          <t>524-35.2423-01</t>
+        </is>
+      </c>
+      <c r="H100" s="16" t="inlineStr"/>
       <c r="I100" s="16" t="inlineStr">
         <is>
           <t>Комплект</t>
@@ -9879,12 +9883,12 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>524-35.2423-01</t>
+          <t>524-03.188</t>
         </is>
       </c>
       <c r="H101" s="16" t="inlineStr"/>
@@ -9895,10 +9899,10 @@
       </c>
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L101" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M101" s="16" t="n">
         <v>0.4</v>
@@ -9966,17 +9970,17 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Ду6</t>
+          <t>Ду10</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>524-03.188</t>
+          <t>521-35.3238</t>
         </is>
       </c>
       <c r="H102" s="16" t="inlineStr"/>
@@ -9987,13 +9991,13 @@
       </c>
       <c r="J102" s="4" t="inlineStr"/>
       <c r="K102" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L102" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M102" s="16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N102" s="17">
         <f>L102*M102</f>
@@ -10015,7 +10019,7 @@
         <v/>
       </c>
       <c r="S102" s="21" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="T102" s="17">
         <f>L102*S102</f>
@@ -10068,7 +10072,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>521-35.3238</t>
+          <t>521-03.420</t>
         </is>
       </c>
       <c r="H103" s="16" t="inlineStr"/>
@@ -10079,10 +10083,10 @@
       </c>
       <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L103" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M103" s="16" t="n">
         <v>0.6</v>
@@ -10092,7 +10096,7 @@
         <v/>
       </c>
       <c r="O103" s="18" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="P103" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N103/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O103/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L103/'Расходы и доставка'!$B$21,T103/'Расходы и доставка'!$B$22))),0)</f>
@@ -10155,12 +10159,12 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>521-03.420</t>
+          <t>525-35.2634</t>
         </is>
       </c>
       <c r="H104" s="16" t="inlineStr"/>
@@ -10171,10 +10175,10 @@
       </c>
       <c r="J104" s="4" t="inlineStr"/>
       <c r="K104" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L104" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M104" s="16" t="n">
         <v>0.6</v>
@@ -10184,7 +10188,7 @@
         <v/>
       </c>
       <c r="O104" s="18" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="P104" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N104/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O104/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L104/'Расходы и доставка'!$B$21,T104/'Расходы и доставка'!$B$22))),0)</f>
@@ -10252,7 +10256,7 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>525-35.2634</t>
+          <t>525-35.2634-04</t>
         </is>
       </c>
       <c r="H105" s="16" t="inlineStr"/>
@@ -10339,12 +10343,12 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>525-35.2634-04</t>
+          <t>524-03.174</t>
         </is>
       </c>
       <c r="H106" s="16" t="inlineStr"/>
@@ -10431,12 +10435,12 @@
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>524-03.174</t>
+          <t>524-03.173</t>
         </is>
       </c>
       <c r="H107" s="16" t="inlineStr"/>
@@ -10518,19 +10522,15 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду15</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
-        </is>
-      </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>524-03.173</t>
-        </is>
-      </c>
+          <t>Клапан штущерный проходной Ду15</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr"/>
       <c r="H108" s="16" t="inlineStr"/>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -10539,20 +10539,20 @@
       </c>
       <c r="J108" s="4" t="inlineStr"/>
       <c r="K108" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="L108" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="M108" s="16" t="n">
         <v>1</v>
-      </c>
-      <c r="L108" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M108" s="16" t="n">
-        <v>0.6</v>
       </c>
       <c r="N108" s="17">
         <f>L108*M108</f>
         <v/>
       </c>
       <c r="O108" s="18" t="n">
-        <v>0.001</v>
+        <v>0.066</v>
       </c>
       <c r="P108" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N108/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O108/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L108/'Расходы и доставка'!$B$21,T108/'Расходы и доставка'!$B$22))),0)</f>
@@ -10567,7 +10567,7 @@
         <v/>
       </c>
       <c r="S108" s="21" t="n">
-        <v>6000</v>
+        <v>9500</v>
       </c>
       <c r="T108" s="17">
         <f>L108*S108</f>
@@ -10584,7 +10584,7 @@
       <c r="W108" s="16" t="inlineStr"/>
       <c r="X108" s="4" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="Y108" s="23" t="inlineStr"/>
@@ -10702,19 +10702,15 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду15</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
-        </is>
-      </c>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t>522-01-493</t>
-        </is>
-      </c>
+          <t>Клапан штуцерный угловой Ду15</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr"/>
       <c r="H110" s="16" t="inlineStr"/>
       <c r="I110" s="16" t="inlineStr">
         <is>
@@ -10723,20 +10719,20 @@
       </c>
       <c r="J110" s="4" t="inlineStr"/>
       <c r="K110" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L110" s="16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M110" s="16" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N110" s="17">
         <f>L110*M110</f>
         <v/>
       </c>
       <c r="O110" s="18" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="P110" s="19">
         <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N110/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O110/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L110/'Расходы и доставка'!$B$21,T110/'Расходы и доставка'!$B$22))),0)</f>
@@ -10751,7 +10747,7 @@
         <v/>
       </c>
       <c r="S110" s="21" t="n">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="T110" s="17">
         <f>L110*S110</f>
@@ -10768,49 +10764,3633 @@
       <c r="W110" s="16" t="inlineStr"/>
       <c r="X110" s="4" t="inlineStr">
         <is>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="Y110" s="23" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>521-01.469-03</t>
+        </is>
+      </c>
+      <c r="H111" s="16" t="inlineStr"/>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr"/>
+      <c r="K111" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L111" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M111" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N111" s="17">
+        <f>L111*M111</f>
+        <v/>
+      </c>
+      <c r="O111" s="18" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="P111" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N111/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O111/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L111/'Расходы и доставка'!$B$21,T111/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q111" s="17">
+        <f>P111*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R111" s="20">
+        <f>IFERROR(Q111/L111,0)</f>
+        <v/>
+      </c>
+      <c r="S111" s="21" t="n">
+        <v>4500</v>
+      </c>
+      <c r="T111" s="17">
+        <f>L111*S111</f>
+        <v/>
+      </c>
+      <c r="U111" s="17">
+        <f>S111+R111</f>
+        <v/>
+      </c>
+      <c r="V111" s="22">
+        <f>IFERROR(R111/S111,"")</f>
+        <v/>
+      </c>
+      <c r="W111" s="16" t="inlineStr"/>
+      <c r="X111" s="4" t="inlineStr">
+        <is>
           <t>Склад 2</t>
         </is>
       </c>
-      <c r="Y110" s="23" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="F111" s="9" t="inlineStr">
+      <c r="Y111" s="23" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>кран</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr"/>
+      <c r="H112" s="16" t="inlineStr"/>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr"/>
+      <c r="K112" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L112" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M112" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" s="17">
+        <f>L112*M112</f>
+        <v/>
+      </c>
+      <c r="O112" s="18" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P112" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N112/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O112/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L112/'Расходы и доставка'!$B$21,T112/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q112" s="17">
+        <f>P112*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R112" s="20">
+        <f>IFERROR(Q112/L112,0)</f>
+        <v/>
+      </c>
+      <c r="S112" s="21" t="n">
+        <v>7500</v>
+      </c>
+      <c r="T112" s="17">
+        <f>L112*S112</f>
+        <v/>
+      </c>
+      <c r="U112" s="17">
+        <f>S112+R112</f>
+        <v/>
+      </c>
+      <c r="V112" s="22">
+        <f>IFERROR(R112/S112,"")</f>
+        <v/>
+      </c>
+      <c r="W112" s="16" t="inlineStr"/>
+      <c r="X112" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y112" s="23" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>522-01-493</t>
+        </is>
+      </c>
+      <c r="H113" s="16" t="inlineStr"/>
+      <c r="I113" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr"/>
+      <c r="K113" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L113" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M113" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N113" s="17">
+        <f>L113*M113</f>
+        <v/>
+      </c>
+      <c r="O113" s="18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P113" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N113/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O113/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L113/'Расходы и доставка'!$B$21,T113/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q113" s="17">
+        <f>P113*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R113" s="20">
+        <f>IFERROR(Q113/L113,0)</f>
+        <v/>
+      </c>
+      <c r="S113" s="21" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T113" s="17">
+        <f>L113*S113</f>
+        <v/>
+      </c>
+      <c r="U113" s="17">
+        <f>S113+R113</f>
+        <v/>
+      </c>
+      <c r="V113" s="22">
+        <f>IFERROR(R113/S113,"")</f>
+        <v/>
+      </c>
+      <c r="W113" s="16" t="inlineStr"/>
+      <c r="X113" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y113" s="23" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>522-01-493-01</t>
+        </is>
+      </c>
+      <c r="H114" s="16" t="inlineStr"/>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr"/>
+      <c r="K114" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N114" s="17">
+        <f>L114*M114</f>
+        <v/>
+      </c>
+      <c r="O114" s="18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P114" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N114/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O114/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L114/'Расходы и доставка'!$B$21,T114/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q114" s="17">
+        <f>P114*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R114" s="20">
+        <f>IFERROR(Q114/L114,0)</f>
+        <v/>
+      </c>
+      <c r="S114" s="21" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T114" s="17">
+        <f>L114*S114</f>
+        <v/>
+      </c>
+      <c r="U114" s="17">
+        <f>S114+R114</f>
+        <v/>
+      </c>
+      <c r="V114" s="22">
+        <f>IFERROR(R114/S114,"")</f>
+        <v/>
+      </c>
+      <c r="W114" s="16" t="inlineStr"/>
+      <c r="X114" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y114" s="23" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>521-35.2754</t>
+        </is>
+      </c>
+      <c r="H115" s="16" t="inlineStr"/>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr"/>
+      <c r="K115" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L115" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M115" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N115" s="17">
+        <f>L115*M115</f>
+        <v/>
+      </c>
+      <c r="O115" s="18" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P115" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N115/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O115/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L115/'Расходы и доставка'!$B$21,T115/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q115" s="17">
+        <f>P115*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R115" s="20">
+        <f>IFERROR(Q115/L115,0)</f>
+        <v/>
+      </c>
+      <c r="S115" s="21" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T115" s="17">
+        <f>L115*S115</f>
+        <v/>
+      </c>
+      <c r="U115" s="17">
+        <f>S115+R115</f>
+        <v/>
+      </c>
+      <c r="V115" s="22">
+        <f>IFERROR(R115/S115,"")</f>
+        <v/>
+      </c>
+      <c r="W115" s="16" t="inlineStr"/>
+      <c r="X115" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y115" s="23" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду10 Р160</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>522-03,149</t>
+        </is>
+      </c>
+      <c r="H116" s="16" t="inlineStr"/>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr"/>
+      <c r="K116" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L116" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M116" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N116" s="17">
+        <f>L116*M116</f>
+        <v/>
+      </c>
+      <c r="O116" s="18" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P116" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N116/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O116/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L116/'Расходы и доставка'!$B$21,T116/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q116" s="17">
+        <f>P116*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R116" s="20">
+        <f>IFERROR(Q116/L116,0)</f>
+        <v/>
+      </c>
+      <c r="S116" s="21" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T116" s="17">
+        <f>L116*S116</f>
+        <v/>
+      </c>
+      <c r="U116" s="17">
+        <f>S116+R116</f>
+        <v/>
+      </c>
+      <c r="V116" s="22">
+        <f>IFERROR(R116/S116,"")</f>
+        <v/>
+      </c>
+      <c r="W116" s="16" t="inlineStr"/>
+      <c r="X116" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y116" s="23" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>522-01.501-01</t>
+        </is>
+      </c>
+      <c r="H117" s="16" t="inlineStr"/>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr"/>
+      <c r="K117" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N117" s="17">
+        <f>L117*M117</f>
+        <v/>
+      </c>
+      <c r="O117" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P117" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N117/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O117/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L117/'Расходы и доставка'!$B$21,T117/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q117" s="17">
+        <f>P117*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R117" s="20">
+        <f>IFERROR(Q117/L117,0)</f>
+        <v/>
+      </c>
+      <c r="S117" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="T117" s="17">
+        <f>L117*S117</f>
+        <v/>
+      </c>
+      <c r="U117" s="17">
+        <f>S117+R117</f>
+        <v/>
+      </c>
+      <c r="V117" s="22">
+        <f>IFERROR(R117/S117,"")</f>
+        <v/>
+      </c>
+      <c r="W117" s="16" t="inlineStr"/>
+      <c r="X117" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y117" s="23" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>521-01.471-02</t>
+        </is>
+      </c>
+      <c r="H118" s="16" t="inlineStr"/>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N118" s="17">
+        <f>L118*M118</f>
+        <v/>
+      </c>
+      <c r="O118" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P118" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N118/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O118/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L118/'Расходы и доставка'!$B$21,T118/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q118" s="17">
+        <f>P118*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R118" s="20">
+        <f>IFERROR(Q118/L118,0)</f>
+        <v/>
+      </c>
+      <c r="S118" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="T118" s="17">
+        <f>L118*S118</f>
+        <v/>
+      </c>
+      <c r="U118" s="17">
+        <f>S118+R118</f>
+        <v/>
+      </c>
+      <c r="V118" s="22">
+        <f>IFERROR(R118/S118,"")</f>
+        <v/>
+      </c>
+      <c r="W118" s="16" t="inlineStr"/>
+      <c r="X118" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y118" s="23" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>521. 3м.666</t>
+        </is>
+      </c>
+      <c r="H119" s="16" t="inlineStr"/>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr"/>
+      <c r="K119" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L119" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M119" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N119" s="17">
+        <f>L119*M119</f>
+        <v/>
+      </c>
+      <c r="O119" s="18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P119" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N119/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O119/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L119/'Расходы и доставка'!$B$21,T119/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q119" s="17">
+        <f>P119*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R119" s="20">
+        <f>IFERROR(Q119/L119,0)</f>
+        <v/>
+      </c>
+      <c r="S119" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="T119" s="17">
+        <f>L119*S119</f>
+        <v/>
+      </c>
+      <c r="U119" s="17">
+        <f>S119+R119</f>
+        <v/>
+      </c>
+      <c r="V119" s="22">
+        <f>IFERROR(R119/S119,"")</f>
+        <v/>
+      </c>
+      <c r="W119" s="16" t="inlineStr"/>
+      <c r="X119" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y119" s="23" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>521-01.470.02</t>
+        </is>
+      </c>
+      <c r="H120" s="16" t="inlineStr"/>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr"/>
+      <c r="K120" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N120" s="17">
+        <f>L120*M120</f>
+        <v/>
+      </c>
+      <c r="O120" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P120" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N120/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O120/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L120/'Расходы и доставка'!$B$21,T120/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q120" s="17">
+        <f>P120*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R120" s="20">
+        <f>IFERROR(Q120/L120,0)</f>
+        <v/>
+      </c>
+      <c r="S120" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="T120" s="17">
+        <f>L120*S120</f>
+        <v/>
+      </c>
+      <c r="U120" s="17">
+        <f>S120+R120</f>
+        <v/>
+      </c>
+      <c r="V120" s="22">
+        <f>IFERROR(R120/S120,"")</f>
+        <v/>
+      </c>
+      <c r="W120" s="16" t="inlineStr"/>
+      <c r="X120" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y120" s="23" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>521 3м.770</t>
+        </is>
+      </c>
+      <c r="H121" s="16" t="inlineStr"/>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N121" s="17">
+        <f>L121*M121</f>
+        <v/>
+      </c>
+      <c r="O121" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P121" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N121/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O121/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L121/'Расходы и доставка'!$B$21,T121/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q121" s="17">
+        <f>P121*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R121" s="20">
+        <f>IFERROR(Q121/L121,0)</f>
+        <v/>
+      </c>
+      <c r="S121" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="T121" s="17">
+        <f>L121*S121</f>
+        <v/>
+      </c>
+      <c r="U121" s="17">
+        <f>S121+R121</f>
+        <v/>
+      </c>
+      <c r="V121" s="22">
+        <f>IFERROR(R121/S121,"")</f>
+        <v/>
+      </c>
+      <c r="W121" s="16" t="inlineStr"/>
+      <c r="X121" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y121" s="23" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>без чертежа</t>
+        </is>
+      </c>
+      <c r="H122" s="16" t="inlineStr"/>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr"/>
+      <c r="K122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N122" s="17">
+        <f>L122*M122</f>
+        <v/>
+      </c>
+      <c r="O122" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P122" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N122/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O122/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L122/'Расходы и доставка'!$B$21,T122/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q122" s="17">
+        <f>P122*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R122" s="20">
+        <f>IFERROR(Q122/L122,0)</f>
+        <v/>
+      </c>
+      <c r="S122" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="T122" s="17">
+        <f>L122*S122</f>
+        <v/>
+      </c>
+      <c r="U122" s="17">
+        <f>S122+R122</f>
+        <v/>
+      </c>
+      <c r="V122" s="22">
+        <f>IFERROR(R122/S122,"")</f>
+        <v/>
+      </c>
+      <c r="W122" s="16" t="inlineStr"/>
+      <c r="X122" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y122" s="23" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>522-01.498</t>
+        </is>
+      </c>
+      <c r="H123" s="16" t="inlineStr"/>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L123" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M123" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N123" s="17">
+        <f>L123*M123</f>
+        <v/>
+      </c>
+      <c r="O123" s="18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P123" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N123/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O123/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L123/'Расходы и доставка'!$B$21,T123/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q123" s="17">
+        <f>P123*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R123" s="20">
+        <f>IFERROR(Q123/L123,0)</f>
+        <v/>
+      </c>
+      <c r="S123" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="T123" s="17">
+        <f>L123*S123</f>
+        <v/>
+      </c>
+      <c r="U123" s="17">
+        <f>S123+R123</f>
+        <v/>
+      </c>
+      <c r="V123" s="22">
+        <f>IFERROR(R123/S123,"")</f>
+        <v/>
+      </c>
+      <c r="W123" s="16" t="inlineStr"/>
+      <c r="X123" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y123" s="23" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>521-01.470</t>
+        </is>
+      </c>
+      <c r="H124" s="16" t="inlineStr"/>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N124" s="17">
+        <f>L124*M124</f>
+        <v/>
+      </c>
+      <c r="O124" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P124" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N124/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O124/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L124/'Расходы и доставка'!$B$21,T124/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q124" s="17">
+        <f>P124*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R124" s="20">
+        <f>IFERROR(Q124/L124,0)</f>
+        <v/>
+      </c>
+      <c r="S124" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="T124" s="17">
+        <f>L124*S124</f>
+        <v/>
+      </c>
+      <c r="U124" s="17">
+        <f>S124+R124</f>
+        <v/>
+      </c>
+      <c r="V124" s="22">
+        <f>IFERROR(R124/S124,"")</f>
+        <v/>
+      </c>
+      <c r="W124" s="16" t="inlineStr"/>
+      <c r="X124" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y124" s="23" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>521-03.479</t>
+        </is>
+      </c>
+      <c r="H125" s="16" t="inlineStr"/>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr"/>
+      <c r="K125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N125" s="17">
+        <f>L125*M125</f>
+        <v/>
+      </c>
+      <c r="O125" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P125" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N125/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O125/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L125/'Расходы и доставка'!$B$21,T125/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q125" s="17">
+        <f>P125*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R125" s="20">
+        <f>IFERROR(Q125/L125,0)</f>
+        <v/>
+      </c>
+      <c r="S125" s="21" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T125" s="17">
+        <f>L125*S125</f>
+        <v/>
+      </c>
+      <c r="U125" s="17">
+        <f>S125+R125</f>
+        <v/>
+      </c>
+      <c r="V125" s="22">
+        <f>IFERROR(R125/S125,"")</f>
+        <v/>
+      </c>
+      <c r="W125" s="16" t="inlineStr"/>
+      <c r="X125" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y125" s="23" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>кран</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>528-3М129</t>
+        </is>
+      </c>
+      <c r="H126" s="16" t="inlineStr"/>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J126" s="4" t="inlineStr"/>
+      <c r="K126" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="L126" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="M126" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N126" s="17">
+        <f>L126*M126</f>
+        <v/>
+      </c>
+      <c r="O126" s="18" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="P126" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N126/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O126/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L126/'Расходы и доставка'!$B$21,T126/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q126" s="17">
+        <f>P126*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R126" s="20">
+        <f>IFERROR(Q126/L126,0)</f>
+        <v/>
+      </c>
+      <c r="S126" s="21" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T126" s="17">
+        <f>L126*S126</f>
+        <v/>
+      </c>
+      <c r="U126" s="17">
+        <f>S126+R126</f>
+        <v/>
+      </c>
+      <c r="V126" s="22">
+        <f>IFERROR(R126/S126,"")</f>
+        <v/>
+      </c>
+      <c r="W126" s="16" t="inlineStr"/>
+      <c r="X126" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y126" s="23" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>кран</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>536-35.695</t>
+        </is>
+      </c>
+      <c r="H127" s="16" t="inlineStr"/>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr"/>
+      <c r="K127" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L127" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M127" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N127" s="17">
+        <f>L127*M127</f>
+        <v/>
+      </c>
+      <c r="O127" s="18" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="P127" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N127/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O127/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L127/'Расходы и доставка'!$B$21,T127/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q127" s="17">
+        <f>P127*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R127" s="20">
+        <f>IFERROR(Q127/L127,0)</f>
+        <v/>
+      </c>
+      <c r="S127" s="21" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T127" s="17">
+        <f>L127*S127</f>
+        <v/>
+      </c>
+      <c r="U127" s="17">
+        <f>S127+R127</f>
+        <v/>
+      </c>
+      <c r="V127" s="22">
+        <f>IFERROR(R127/S127,"")</f>
+        <v/>
+      </c>
+      <c r="W127" s="16" t="inlineStr"/>
+      <c r="X127" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y127" s="23" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15Ру40</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>521-01.465-02</t>
+        </is>
+      </c>
+      <c r="H128" s="16" t="inlineStr"/>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr"/>
+      <c r="K128" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M128" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" s="17">
+        <f>L128*M128</f>
+        <v/>
+      </c>
+      <c r="O128" s="18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P128" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N128/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O128/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L128/'Расходы и доставка'!$B$21,T128/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q128" s="17">
+        <f>P128*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R128" s="20">
+        <f>IFERROR(Q128/L128,0)</f>
+        <v/>
+      </c>
+      <c r="S128" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T128" s="17">
+        <f>L128*S128</f>
+        <v/>
+      </c>
+      <c r="U128" s="17">
+        <f>S128+R128</f>
+        <v/>
+      </c>
+      <c r="V128" s="22">
+        <f>IFERROR(R128/S128,"")</f>
+        <v/>
+      </c>
+      <c r="W128" s="16" t="inlineStr"/>
+      <c r="X128" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y128" s="23" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>522-01.500-04</t>
+        </is>
+      </c>
+      <c r="H129" s="16" t="inlineStr"/>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr"/>
+      <c r="K129" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L129" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M129" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N129" s="17">
+        <f>L129*M129</f>
+        <v/>
+      </c>
+      <c r="O129" s="18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P129" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N129/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O129/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L129/'Расходы и доставка'!$B$21,T129/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q129" s="17">
+        <f>P129*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R129" s="20">
+        <f>IFERROR(Q129/L129,0)</f>
+        <v/>
+      </c>
+      <c r="S129" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T129" s="17">
+        <f>L129*S129</f>
+        <v/>
+      </c>
+      <c r="U129" s="17">
+        <f>S129+R129</f>
+        <v/>
+      </c>
+      <c r="V129" s="22">
+        <f>IFERROR(R129/S129,"")</f>
+        <v/>
+      </c>
+      <c r="W129" s="16" t="inlineStr"/>
+      <c r="X129" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y129" s="23" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>521-01.464-01</t>
+        </is>
+      </c>
+      <c r="H130" s="16" t="inlineStr"/>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr"/>
+      <c r="K130" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L130" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M130" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N130" s="17">
+        <f>L130*M130</f>
+        <v/>
+      </c>
+      <c r="O130" s="18" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="P130" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N130/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O130/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L130/'Расходы и доставка'!$B$21,T130/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q130" s="17">
+        <f>P130*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R130" s="20">
+        <f>IFERROR(Q130/L130,0)</f>
+        <v/>
+      </c>
+      <c r="S130" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T130" s="17">
+        <f>L130*S130</f>
+        <v/>
+      </c>
+      <c r="U130" s="17">
+        <f>S130+R130</f>
+        <v/>
+      </c>
+      <c r="V130" s="22">
+        <f>IFERROR(R130/S130,"")</f>
+        <v/>
+      </c>
+      <c r="W130" s="16" t="inlineStr"/>
+      <c r="X130" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y130" s="23" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>521-01.468</t>
+        </is>
+      </c>
+      <c r="H131" s="16" t="inlineStr"/>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr"/>
+      <c r="K131" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L131" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M131" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N131" s="17">
+        <f>L131*M131</f>
+        <v/>
+      </c>
+      <c r="O131" s="18" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="P131" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N131/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O131/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L131/'Расходы и доставка'!$B$21,T131/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q131" s="17">
+        <f>P131*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R131" s="20">
+        <f>IFERROR(Q131/L131,0)</f>
+        <v/>
+      </c>
+      <c r="S131" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T131" s="17">
+        <f>L131*S131</f>
+        <v/>
+      </c>
+      <c r="U131" s="17">
+        <f>S131+R131</f>
+        <v/>
+      </c>
+      <c r="V131" s="22">
+        <f>IFERROR(R131/S131,"")</f>
+        <v/>
+      </c>
+      <c r="W131" s="16" t="inlineStr"/>
+      <c r="X131" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y131" s="23" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>521-01.468-05</t>
+        </is>
+      </c>
+      <c r="H132" s="16" t="inlineStr"/>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr"/>
+      <c r="K132" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L132" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="M132" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" s="17">
+        <f>L132*M132</f>
+        <v/>
+      </c>
+      <c r="O132" s="18" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P132" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N132/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O132/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L132/'Расходы и доставка'!$B$21,T132/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q132" s="17">
+        <f>P132*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R132" s="20">
+        <f>IFERROR(Q132/L132,0)</f>
+        <v/>
+      </c>
+      <c r="S132" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T132" s="17">
+        <f>L132*S132</f>
+        <v/>
+      </c>
+      <c r="U132" s="17">
+        <f>S132+R132</f>
+        <v/>
+      </c>
+      <c r="V132" s="22">
+        <f>IFERROR(R132/S132,"")</f>
+        <v/>
+      </c>
+      <c r="W132" s="16" t="inlineStr"/>
+      <c r="X132" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y132" s="23" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>521-35.3362</t>
+        </is>
+      </c>
+      <c r="H133" s="16" t="inlineStr"/>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr"/>
+      <c r="K133" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L133" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M133" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" s="17">
+        <f>L133*M133</f>
+        <v/>
+      </c>
+      <c r="O133" s="18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P133" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N133/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O133/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L133/'Расходы и доставка'!$B$21,T133/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q133" s="17">
+        <f>P133*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R133" s="20">
+        <f>IFERROR(Q133/L133,0)</f>
+        <v/>
+      </c>
+      <c r="S133" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T133" s="17">
+        <f>L133*S133</f>
+        <v/>
+      </c>
+      <c r="U133" s="17">
+        <f>S133+R133</f>
+        <v/>
+      </c>
+      <c r="V133" s="22">
+        <f>IFERROR(R133/S133,"")</f>
+        <v/>
+      </c>
+      <c r="W133" s="16" t="inlineStr"/>
+      <c r="X133" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y133" s="23" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>521-01.464-02</t>
+        </is>
+      </c>
+      <c r="H134" s="16" t="inlineStr"/>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr"/>
+      <c r="K134" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N134" s="17">
+        <f>L134*M134</f>
+        <v/>
+      </c>
+      <c r="O134" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P134" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N134/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O134/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L134/'Расходы и доставка'!$B$21,T134/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q134" s="17">
+        <f>P134*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R134" s="20">
+        <f>IFERROR(Q134/L134,0)</f>
+        <v/>
+      </c>
+      <c r="S134" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T134" s="17">
+        <f>L134*S134</f>
+        <v/>
+      </c>
+      <c r="U134" s="17">
+        <f>S134+R134</f>
+        <v/>
+      </c>
+      <c r="V134" s="22">
+        <f>IFERROR(R134/S134,"")</f>
+        <v/>
+      </c>
+      <c r="W134" s="16" t="inlineStr"/>
+      <c r="X134" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y134" s="23" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>522-01.500-05</t>
+        </is>
+      </c>
+      <c r="H135" s="16" t="inlineStr"/>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr"/>
+      <c r="K135" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L135" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M135" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N135" s="17">
+        <f>L135*M135</f>
+        <v/>
+      </c>
+      <c r="O135" s="18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P135" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N135/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O135/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L135/'Расходы и доставка'!$B$21,T135/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q135" s="17">
+        <f>P135*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R135" s="20">
+        <f>IFERROR(Q135/L135,0)</f>
+        <v/>
+      </c>
+      <c r="S135" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T135" s="17">
+        <f>L135*S135</f>
+        <v/>
+      </c>
+      <c r="U135" s="17">
+        <f>S135+R135</f>
+        <v/>
+      </c>
+      <c r="V135" s="22">
+        <f>IFERROR(R135/S135,"")</f>
+        <v/>
+      </c>
+      <c r="W135" s="16" t="inlineStr"/>
+      <c r="X135" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y135" s="23" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>522-01.500-04</t>
+        </is>
+      </c>
+      <c r="H136" s="16" t="inlineStr"/>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr"/>
+      <c r="K136" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M136" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N136" s="17">
+        <f>L136*M136</f>
+        <v/>
+      </c>
+      <c r="O136" s="18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="P136" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N136/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O136/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L136/'Расходы и доставка'!$B$21,T136/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q136" s="17">
+        <f>P136*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R136" s="20">
+        <f>IFERROR(Q136/L136,0)</f>
+        <v/>
+      </c>
+      <c r="S136" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T136" s="17">
+        <f>L136*S136</f>
+        <v/>
+      </c>
+      <c r="U136" s="17">
+        <f>S136+R136</f>
+        <v/>
+      </c>
+      <c r="V136" s="22">
+        <f>IFERROR(R136/S136,"")</f>
+        <v/>
+      </c>
+      <c r="W136" s="16" t="inlineStr"/>
+      <c r="X136" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y136" s="23" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру100</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>521-01.468-01</t>
+        </is>
+      </c>
+      <c r="H137" s="16" t="inlineStr"/>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr"/>
+      <c r="K137" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" s="17">
+        <f>L137*M137</f>
+        <v/>
+      </c>
+      <c r="O137" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P137" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N137/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O137/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L137/'Расходы и доставка'!$B$21,T137/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q137" s="17">
+        <f>P137*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R137" s="20">
+        <f>IFERROR(Q137/L137,0)</f>
+        <v/>
+      </c>
+      <c r="S137" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T137" s="17">
+        <f>L137*S137</f>
+        <v/>
+      </c>
+      <c r="U137" s="17">
+        <f>S137+R137</f>
+        <v/>
+      </c>
+      <c r="V137" s="22">
+        <f>IFERROR(R137/S137,"")</f>
+        <v/>
+      </c>
+      <c r="W137" s="16" t="inlineStr"/>
+      <c r="X137" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y137" s="23" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>525-03.011</t>
+        </is>
+      </c>
+      <c r="H138" s="16" t="inlineStr"/>
+      <c r="I138" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr"/>
+      <c r="K138" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L138" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M138" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" s="17">
+        <f>L138*M138</f>
+        <v/>
+      </c>
+      <c r="O138" s="18" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P138" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N138/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O138/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L138/'Расходы и доставка'!$B$21,T138/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q138" s="17">
+        <f>P138*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R138" s="20">
+        <f>IFERROR(Q138/L138,0)</f>
+        <v/>
+      </c>
+      <c r="S138" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T138" s="17">
+        <f>L138*S138</f>
+        <v/>
+      </c>
+      <c r="U138" s="17">
+        <f>S138+R138</f>
+        <v/>
+      </c>
+      <c r="V138" s="22">
+        <f>IFERROR(R138/S138,"")</f>
+        <v/>
+      </c>
+      <c r="W138" s="16" t="inlineStr"/>
+      <c r="X138" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y138" s="23" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>521-01.471-01</t>
+        </is>
+      </c>
+      <c r="H139" s="16" t="inlineStr"/>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr"/>
+      <c r="K139" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L139" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="M139" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N139" s="17">
+        <f>L139*M139</f>
+        <v/>
+      </c>
+      <c r="O139" s="18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P139" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N139/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O139/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L139/'Расходы и доставка'!$B$21,T139/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q139" s="17">
+        <f>P139*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R139" s="20">
+        <f>IFERROR(Q139/L139,0)</f>
+        <v/>
+      </c>
+      <c r="S139" s="21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T139" s="17">
+        <f>L139*S139</f>
+        <v/>
+      </c>
+      <c r="U139" s="17">
+        <f>S139+R139</f>
+        <v/>
+      </c>
+      <c r="V139" s="22">
+        <f>IFERROR(R139/S139,"")</f>
+        <v/>
+      </c>
+      <c r="W139" s="16" t="inlineStr"/>
+      <c r="X139" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y139" s="23" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>Ду25</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Клапан педальный Ду25</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>М528-03.001</t>
+        </is>
+      </c>
+      <c r="H140" s="16" t="inlineStr"/>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr"/>
+      <c r="K140" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N140" s="17">
+        <f>L140*M140</f>
+        <v/>
+      </c>
+      <c r="O140" s="18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P140" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N140/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O140/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L140/'Расходы и доставка'!$B$21,T140/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q140" s="17">
+        <f>P140*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R140" s="20">
+        <f>IFERROR(Q140/L140,0)</f>
+        <v/>
+      </c>
+      <c r="S140" s="21" t="n">
+        <v>12500</v>
+      </c>
+      <c r="T140" s="17">
+        <f>L140*S140</f>
+        <v/>
+      </c>
+      <c r="U140" s="17">
+        <f>S140+R140</f>
+        <v/>
+      </c>
+      <c r="V140" s="22">
+        <f>IFERROR(R140/S140,"")</f>
+        <v/>
+      </c>
+      <c r="W140" s="16" t="inlineStr"/>
+      <c r="X140" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y140" s="23" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Ду6</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду6Ру100</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>521-01.467-02</t>
+        </is>
+      </c>
+      <c r="H141" s="16" t="inlineStr"/>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr"/>
+      <c r="K141" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L141" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M141" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N141" s="17">
+        <f>L141*M141</f>
+        <v/>
+      </c>
+      <c r="O141" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P141" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N141/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O141/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L141/'Расходы и доставка'!$B$21,T141/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q141" s="17">
+        <f>P141*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R141" s="20">
+        <f>IFERROR(Q141/L141,0)</f>
+        <v/>
+      </c>
+      <c r="S141" s="21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T141" s="17">
+        <f>L141*S141</f>
+        <v/>
+      </c>
+      <c r="U141" s="17">
+        <f>S141+R141</f>
+        <v/>
+      </c>
+      <c r="V141" s="22">
+        <f>IFERROR(R141/S141,"")</f>
+        <v/>
+      </c>
+      <c r="W141" s="16" t="inlineStr"/>
+      <c r="X141" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y141" s="23" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>536-3м 5</t>
+        </is>
+      </c>
+      <c r="H142" s="16" t="inlineStr"/>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr"/>
+      <c r="K142" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L142" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M142" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N142" s="17">
+        <f>L142*M142</f>
+        <v/>
+      </c>
+      <c r="O142" s="18" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="P142" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N142/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O142/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L142/'Расходы и доставка'!$B$21,T142/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q142" s="17">
+        <f>P142*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R142" s="20">
+        <f>IFERROR(Q142/L142,0)</f>
+        <v/>
+      </c>
+      <c r="S142" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="T142" s="17">
+        <f>L142*S142</f>
+        <v/>
+      </c>
+      <c r="U142" s="17">
+        <f>S142+R142</f>
+        <v/>
+      </c>
+      <c r="V142" s="22">
+        <f>IFERROR(R142/S142,"")</f>
+        <v/>
+      </c>
+      <c r="W142" s="16" t="inlineStr"/>
+      <c r="X142" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y142" s="23" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>521-01.469-02</t>
+        </is>
+      </c>
+      <c r="H143" s="16" t="inlineStr"/>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr"/>
+      <c r="K143" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L143" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M143" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N143" s="17">
+        <f>L143*M143</f>
+        <v/>
+      </c>
+      <c r="O143" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P143" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N143/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O143/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L143/'Расходы и доставка'!$B$21,T143/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q143" s="17">
+        <f>P143*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R143" s="20">
+        <f>IFERROR(Q143/L143,0)</f>
+        <v/>
+      </c>
+      <c r="S143" s="21" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T143" s="17">
+        <f>L143*S143</f>
+        <v/>
+      </c>
+      <c r="U143" s="17">
+        <f>S143+R143</f>
+        <v/>
+      </c>
+      <c r="V143" s="22">
+        <f>IFERROR(R143/S143,"")</f>
+        <v/>
+      </c>
+      <c r="W143" s="16" t="inlineStr"/>
+      <c r="X143" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y143" s="23" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>кран</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>Ду32</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>536-35.696</t>
+        </is>
+      </c>
+      <c r="H144" s="16" t="inlineStr"/>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr"/>
+      <c r="K144" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L144" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M144" s="16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N144" s="17">
+        <f>L144*M144</f>
+        <v/>
+      </c>
+      <c r="O144" s="18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P144" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N144/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O144/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L144/'Расходы и доставка'!$B$21,T144/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q144" s="17">
+        <f>P144*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R144" s="20">
+        <f>IFERROR(Q144/L144,0)</f>
+        <v/>
+      </c>
+      <c r="S144" s="21" t="n">
+        <v>14400</v>
+      </c>
+      <c r="T144" s="17">
+        <f>L144*S144</f>
+        <v/>
+      </c>
+      <c r="U144" s="17">
+        <f>S144+R144</f>
+        <v/>
+      </c>
+      <c r="V144" s="22">
+        <f>IFERROR(R144/S144,"")</f>
+        <v/>
+      </c>
+      <c r="W144" s="16" t="inlineStr"/>
+      <c r="X144" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y144" s="23" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>522-03.089</t>
+        </is>
+      </c>
+      <c r="H145" s="16" t="inlineStr"/>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr"/>
+      <c r="K145" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N145" s="17">
+        <f>L145*M145</f>
+        <v/>
+      </c>
+      <c r="O145" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P145" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N145/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O145/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L145/'Расходы и доставка'!$B$21,T145/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q145" s="17">
+        <f>P145*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R145" s="20">
+        <f>IFERROR(Q145/L145,0)</f>
+        <v/>
+      </c>
+      <c r="S145" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T145" s="17">
+        <f>L145*S145</f>
+        <v/>
+      </c>
+      <c r="U145" s="17">
+        <f>S145+R145</f>
+        <v/>
+      </c>
+      <c r="V145" s="22">
+        <f>IFERROR(R145/S145,"")</f>
+        <v/>
+      </c>
+      <c r="W145" s="16" t="inlineStr"/>
+      <c r="X145" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y145" s="23" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>536 3м .333</t>
+        </is>
+      </c>
+      <c r="H146" s="16" t="inlineStr"/>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr"/>
+      <c r="K146" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N146" s="17">
+        <f>L146*M146</f>
+        <v/>
+      </c>
+      <c r="O146" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P146" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N146/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O146/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L146/'Расходы и доставка'!$B$21,T146/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q146" s="17">
+        <f>P146*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R146" s="20">
+        <f>IFERROR(Q146/L146,0)</f>
+        <v/>
+      </c>
+      <c r="S146" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T146" s="17">
+        <f>L146*S146</f>
+        <v/>
+      </c>
+      <c r="U146" s="17">
+        <f>S146+R146</f>
+        <v/>
+      </c>
+      <c r="V146" s="22">
+        <f>IFERROR(R146/S146,"")</f>
+        <v/>
+      </c>
+      <c r="W146" s="16" t="inlineStr"/>
+      <c r="X146" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y146" s="23" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>521 3м 726</t>
+        </is>
+      </c>
+      <c r="H147" s="16" t="inlineStr"/>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr"/>
+      <c r="K147" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L147" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M147" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N147" s="17">
+        <f>L147*M147</f>
+        <v/>
+      </c>
+      <c r="O147" s="18" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="P147" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N147/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O147/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L147/'Расходы и доставка'!$B$21,T147/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q147" s="17">
+        <f>P147*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R147" s="20">
+        <f>IFERROR(Q147/L147,0)</f>
+        <v/>
+      </c>
+      <c r="S147" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T147" s="17">
+        <f>L147*S147</f>
+        <v/>
+      </c>
+      <c r="U147" s="17">
+        <f>S147+R147</f>
+        <v/>
+      </c>
+      <c r="V147" s="22">
+        <f>IFERROR(R147/S147,"")</f>
+        <v/>
+      </c>
+      <c r="W147" s="16" t="inlineStr"/>
+      <c r="X147" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y147" s="23" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>521 3м 30</t>
+        </is>
+      </c>
+      <c r="H148" s="16" t="inlineStr"/>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr"/>
+      <c r="K148" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N148" s="17">
+        <f>L148*M148</f>
+        <v/>
+      </c>
+      <c r="O148" s="18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="P148" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N148/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O148/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L148/'Расходы и доставка'!$B$21,T148/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q148" s="17">
+        <f>P148*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R148" s="20">
+        <f>IFERROR(Q148/L148,0)</f>
+        <v/>
+      </c>
+      <c r="S148" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T148" s="17">
+        <f>L148*S148</f>
+        <v/>
+      </c>
+      <c r="U148" s="17">
+        <f>S148+R148</f>
+        <v/>
+      </c>
+      <c r="V148" s="22">
+        <f>IFERROR(R148/S148,"")</f>
+        <v/>
+      </c>
+      <c r="W148" s="16" t="inlineStr"/>
+      <c r="X148" s="4" t="inlineStr">
+        <is>
+          <t>Менеджерская</t>
+        </is>
+      </c>
+      <c r="Y148" s="23" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру6</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>521-3м-52</t>
+        </is>
+      </c>
+      <c r="H149" s="16" t="inlineStr"/>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>Комплект</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr"/>
+      <c r="K149" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N149" s="17">
+        <f>L149*M149</f>
+        <v/>
+      </c>
+      <c r="O149" s="18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P149" s="19">
+        <f>IFERROR(IF('Расходы и доставка'!$B$15="по весу",N149/'Расходы и доставка'!$B$19,IF('Расходы и доставка'!$B$15="по объему",O149/'Расходы и доставка'!$B$20,IF('Расходы и доставка'!$B$15="поровну на штуку",L149/'Расходы и доставка'!$B$21,T149/'Расходы и доставка'!$B$22))),0)</f>
+        <v/>
+      </c>
+      <c r="Q149" s="17">
+        <f>P149*'Расходы и доставка'!$B$13</f>
+        <v/>
+      </c>
+      <c r="R149" s="20">
+        <f>IFERROR(Q149/L149,0)</f>
+        <v/>
+      </c>
+      <c r="S149" s="21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T149" s="17">
+        <f>L149*S149</f>
+        <v/>
+      </c>
+      <c r="U149" s="17">
+        <f>S149+R149</f>
+        <v/>
+      </c>
+      <c r="V149" s="22">
+        <f>IFERROR(R149/S149,"")</f>
+        <v/>
+      </c>
+      <c r="W149" s="16" t="inlineStr"/>
+      <c r="X149" s="4" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="Y149" s="23" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="F150" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="K111" s="24">
-        <f>SUM(K5:K110)</f>
-        <v/>
-      </c>
-      <c r="L111" s="24">
-        <f>SUM(L5:L110)</f>
-        <v/>
-      </c>
-      <c r="N111" s="24">
-        <f>SUM(N5:N110)</f>
-        <v/>
-      </c>
-      <c r="O111" s="25">
-        <f>SUM(O5:O110)</f>
-        <v/>
-      </c>
-      <c r="Q111" s="24">
-        <f>SUM(Q5:Q110)</f>
-        <v/>
-      </c>
-      <c r="T111" s="24">
-        <f>SUM(T5:T110)</f>
+      <c r="K150" s="24">
+        <f>SUM(K5:K149)</f>
+        <v/>
+      </c>
+      <c r="L150" s="24">
+        <f>SUM(L5:L149)</f>
+        <v/>
+      </c>
+      <c r="N150" s="24">
+        <f>SUM(N5:N149)</f>
+        <v/>
+      </c>
+      <c r="O150" s="25">
+        <f>SUM(O5:O149)</f>
+        <v/>
+      </c>
+      <c r="Q150" s="24">
+        <f>SUM(Q5:Q149)</f>
+        <v/>
+      </c>
+      <c r="T150" s="24">
+        <f>SUM(T5:T149)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Y110"/>
+  <autoFilter ref="A4:Y149"/>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Новое,Б/у,Восстановленное"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Комплект,Не комплект,Брак"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10894,23 +14474,23 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF('Отгрузка'!H$5:H$110,"Новое")</f>
+        <f>COUNTIF('Отгрузка'!H$5:H$149,"Новое")</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Новое",'Отгрузка'!L$5:L$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Новое",'Отгрузка'!L$5:L$149)</f>
         <v/>
       </c>
       <c r="D5" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Новое",'Отгрузка'!N$5:N$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Новое",'Отгрузка'!N$5:N$149)</f>
         <v/>
       </c>
       <c r="E5" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Новое",'Отгрузка'!T$5:T$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Новое",'Отгрузка'!T$5:T$149)</f>
         <v/>
       </c>
       <c r="F5" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Новое",'Отгрузка'!Q$5:Q$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Новое",'Отгрузка'!Q$5:Q$149)</f>
         <v/>
       </c>
       <c r="G5" s="26">
@@ -10925,23 +14505,23 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF('Отгрузка'!H$5:H$110,"Б/у")</f>
+        <f>COUNTIF('Отгрузка'!H$5:H$149,"Б/у")</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Б/у",'Отгрузка'!L$5:L$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Б/у",'Отгрузка'!L$5:L$149)</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Б/у",'Отгрузка'!N$5:N$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Б/у",'Отгрузка'!N$5:N$149)</f>
         <v/>
       </c>
       <c r="E6" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Б/у",'Отгрузка'!T$5:T$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Б/у",'Отгрузка'!T$5:T$149)</f>
         <v/>
       </c>
       <c r="F6" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Б/у",'Отгрузка'!Q$5:Q$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Б/у",'Отгрузка'!Q$5:Q$149)</f>
         <v/>
       </c>
       <c r="G6" s="26">
@@ -10956,23 +14536,23 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF('Отгрузка'!H$5:H$110,"Восстановленное")</f>
+        <f>COUNTIF('Отгрузка'!H$5:H$149,"Восстановленное")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Восстановленное",'Отгрузка'!L$5:L$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Восстановленное",'Отгрузка'!L$5:L$149)</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Восстановленное",'Отгрузка'!N$5:N$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Восстановленное",'Отгрузка'!N$5:N$149)</f>
         <v/>
       </c>
       <c r="E7" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Восстановленное",'Отгрузка'!T$5:T$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Восстановленное",'Отгрузка'!T$5:T$149)</f>
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"Восстановленное",'Отгрузка'!Q$5:Q$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"Восстановленное",'Отгрузка'!Q$5:Q$149)</f>
         <v/>
       </c>
       <c r="G7" s="26">
@@ -10987,23 +14567,23 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTBLANK('Отгрузка'!H$5:H$110)</f>
+        <f>COUNTBLANK('Отгрузка'!H$5:H$149)</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"",'Отгрузка'!L$5:L$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"",'Отгрузка'!L$5:L$149)</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"",'Отгрузка'!N$5:N$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"",'Отгрузка'!N$5:N$149)</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"",'Отгрузка'!T$5:T$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"",'Отгрузка'!T$5:T$149)</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>SUMIF('Отгрузка'!H$5:H$110,"",'Отгрузка'!Q$5:Q$110)</f>
+        <f>SUMIF('Отгрузка'!H$5:H$149,"",'Отгрузка'!Q$5:Q$149)</f>
         <v/>
       </c>
       <c r="G8" s="26">
@@ -11056,7 +14636,7 @@
         </is>
       </c>
       <c r="B12" s="24">
-        <f>SUM('Отгрузка'!Q$5:Q$110)</f>
+        <f>SUM('Отгрузка'!Q$5:Q$149)</f>
         <v/>
       </c>
     </row>
@@ -11078,7 +14658,7 @@
         </is>
       </c>
       <c r="B14" s="24">
-        <f>SUM('Отгрузка'!Q$5:Q$110)-'Расходы и доставка'!$B$13</f>
+        <f>SUM('Отгрузка'!Q$5:Q$149)-'Расходы и доставка'!$B$13</f>
         <v/>
       </c>
     </row>

--- a/outputs/marine_equipment/Отгрузка_Питер_учет.xlsx
+++ b/outputs/marine_equipment/Отгрузка_Питер_учет.xlsx
@@ -3491,7 +3491,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr"/>
@@ -8685,7 +8685,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан паровой</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr"/>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан педальный</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">

--- a/outputs/marine_equipment/Отгрузка_Питер_учет.xlsx
+++ b/outputs/marine_equipment/Отгрузка_Питер_учет.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
